--- a/TestFiles-prod-sanity/StatementUpload/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
+++ b/TestFiles-prod-sanity/StatementUpload/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
@@ -630,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="9">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>29</v>
